--- a/backend/data/csv_import/Central_Parity_Historical_Data_2026.xlsx
+++ b/backend/data/csv_import/Central_Parity_Historical_Data_2026.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B103"/>
+  <dimension ref="A1:B111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -431,1218 +431,1314 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>05 Jun 2026</t>
+          <t>17 Jun 2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>6.8157</t>
+          <t>6.8096</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>04 Jun 2026</t>
+          <t>16 Jun 2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>6.8203</t>
+          <t>6.8108</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>03 Jun 2026</t>
+          <t>15 Jun 2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>6.8184</t>
+          <t>6.8088</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>02 Jun 2026</t>
+          <t>12 Jun 2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6.8187</t>
+          <t>6.8109</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>01 Jun 2026</t>
+          <t>11 Jun 2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>6.8167</t>
+          <t>6.815</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>29 May 2026</t>
+          <t>10 Jun 2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>6.8176</t>
+          <t>6.813</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>28 May 2026</t>
+          <t>09 Jun 2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>6.824</t>
+          <t>6.8147</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>27 May 2026</t>
+          <t>08 Jun 2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>6.8291</t>
+          <t>6.8198</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>26 May 2026</t>
+          <t>05 Jun 2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>6.8288</t>
+          <t>6.8157</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>25 May 2026</t>
+          <t>04 Jun 2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>6.8318</t>
+          <t>6.8203</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>22 May 2026</t>
+          <t>03 Jun 2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>6.8373</t>
+          <t>6.8184</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>21 May 2026</t>
+          <t>02 Jun 2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>6.8349</t>
+          <t>6.8187</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20 May 2026</t>
+          <t>01 Jun 2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>6.8397</t>
+          <t>6.8167</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>19 May 2026</t>
+          <t>29 May 2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>6.8375</t>
+          <t>6.8176</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>18 May 2026</t>
+          <t>28 May 2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>6.8435</t>
+          <t>6.824</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>15 May 2026</t>
+          <t>27 May 2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>6.8415</t>
+          <t>6.8291</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>14 May 2026</t>
+          <t>26 May 2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>6.8401</t>
+          <t>6.8288</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>13 May 2026</t>
+          <t>25 May 2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>6.8431</t>
+          <t>6.8318</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>12 May 2026</t>
+          <t>22 May 2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>6.8426</t>
+          <t>6.8373</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>11 May 2026</t>
+          <t>21 May 2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>6.8467</t>
+          <t>6.8349</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>08 May 2026</t>
+          <t>20 May 2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>6.8502</t>
+          <t>6.8397</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07 May 2026</t>
+          <t>19 May 2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>6.8487</t>
+          <t>6.8375</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>06 May 2026</t>
+          <t>18 May 2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>6.8562</t>
+          <t>6.8435</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>30 Apr 2026</t>
+          <t>15 May 2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>6.8628</t>
+          <t>6.8415</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>29 Apr 2026</t>
+          <t>14 May 2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>6.8608</t>
+          <t>6.8401</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>28 Apr 2026</t>
+          <t>13 May 2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>6.8589</t>
+          <t>6.8431</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>27 Apr 2026</t>
+          <t>12 May 2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>6.8579</t>
+          <t>6.8426</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>24 Apr 2026</t>
+          <t>11 May 2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>6.8674</t>
+          <t>6.8467</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>23 Apr 2026</t>
+          <t>08 May 2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>6.865</t>
+          <t>6.8502</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>22 Apr 2026</t>
+          <t>07 May 2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>6.8635</t>
+          <t>6.8487</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>21 Apr 2026</t>
+          <t>06 May 2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>6.8594</t>
+          <t>6.8562</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>20 Apr 2026</t>
+          <t>30 Apr 2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>6.8648</t>
+          <t>6.8628</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>17 Apr 2026</t>
+          <t>29 Apr 2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>6.8622</t>
+          <t>6.8608</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>16 Apr 2026</t>
+          <t>28 Apr 2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>6.8616</t>
+          <t>6.8589</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>15 Apr 2026</t>
+          <t>27 Apr 2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>6.8582</t>
+          <t>6.8579</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>14 Apr 2026</t>
+          <t>24 Apr 2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>6.8593</t>
+          <t>6.8674</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>13 Apr 2026</t>
+          <t>23 Apr 2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>6.8657</t>
+          <t>6.865</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>10 Apr 2026</t>
+          <t>22 Apr 2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>6.8654</t>
+          <t>6.8635</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>09 Apr 2026</t>
+          <t>21 Apr 2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>6.8649</t>
+          <t>6.8594</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>08 Apr 2026</t>
+          <t>20 Apr 2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>6.868</t>
+          <t>6.8648</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07 Apr 2026</t>
+          <t>17 Apr 2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>6.8854</t>
+          <t>6.8622</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>03 Apr 2026</t>
+          <t>16 Apr 2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>6.8929</t>
+          <t>6.8616</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>02 Apr 2026</t>
+          <t>15 Apr 2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>6.888</t>
+          <t>6.8582</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>01 Apr 2026</t>
+          <t>14 Apr 2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>6.9025</t>
+          <t>6.8593</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>31 Mar 2026</t>
+          <t>13 Apr 2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>6.9194</t>
+          <t>6.8657</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>30 Mar 2026</t>
+          <t>10 Apr 2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>6.9223</t>
+          <t>6.8654</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>27 Mar 2026</t>
+          <t>09 Apr 2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>6.9141</t>
+          <t>6.8649</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>26 Mar 2026</t>
+          <t>08 Apr 2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>6.9056</t>
+          <t>6.868</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>25 Mar 2026</t>
+          <t>07 Apr 2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>6.8911</t>
+          <t>6.8854</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>24 Mar 2026</t>
+          <t>03 Apr 2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>6.8943</t>
+          <t>6.8929</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>23 Mar 2026</t>
+          <t>02 Apr 2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>6.9041</t>
+          <t>6.888</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>20 Mar 2026</t>
+          <t>01 Apr 2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>6.8898</t>
+          <t>6.9025</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>19 Mar 2026</t>
+          <t>31 Mar 2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>6.8975</t>
+          <t>6.9194</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>18 Mar 2026</t>
+          <t>30 Mar 2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>6.8909</t>
+          <t>6.9223</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>17 Mar 2026</t>
+          <t>27 Mar 2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>6.8961</t>
+          <t>6.9141</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>16 Mar 2026</t>
+          <t>26 Mar 2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>6.9057</t>
+          <t>6.9056</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>13 Mar 2026</t>
+          <t>25 Mar 2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>6.9007</t>
+          <t>6.8911</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>12 Mar 2026</t>
+          <t>24 Mar 2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>6.8959</t>
+          <t>6.8943</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>11 Mar 2026</t>
+          <t>23 Mar 2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>6.8917</t>
+          <t>6.9041</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>10 Mar 2026</t>
+          <t>20 Mar 2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>6.8982</t>
+          <t>6.8898</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>09 Mar 2026</t>
+          <t>19 Mar 2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>6.9158</t>
+          <t>6.8975</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>06 Mar 2026</t>
+          <t>18 Mar 2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>6.9025</t>
+          <t>6.8909</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>05 Mar 2026</t>
+          <t>17 Mar 2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>6.9007</t>
+          <t>6.8961</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>04 Mar 2026</t>
+          <t>16 Mar 2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>6.9124</t>
+          <t>6.9057</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>03 Mar 2026</t>
+          <t>13 Mar 2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>6.9088</t>
+          <t>6.9007</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>02 Mar 2026</t>
+          <t>12 Mar 2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>6.9236</t>
+          <t>6.8959</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>27 Feb 2026</t>
+          <t>11 Mar 2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>6.9228</t>
+          <t>6.8917</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>26 Feb 2026</t>
+          <t>10 Mar 2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>6.9228</t>
+          <t>6.8982</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>25 Feb 2026</t>
+          <t>09 Mar 2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>6.9321</t>
+          <t>6.9158</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>24 Feb 2026</t>
+          <t>06 Mar 2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>6.9414</t>
+          <t>6.9025</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>13 Feb 2026</t>
+          <t>05 Mar 2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>6.9398</t>
+          <t>6.9007</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>12 Feb 2026</t>
+          <t>04 Mar 2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>6.9457</t>
+          <t>6.9124</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>11 Feb 2026</t>
+          <t>03 Mar 2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>6.9438</t>
+          <t>6.9088</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>10 Feb 2026</t>
+          <t>02 Mar 2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>6.9458</t>
+          <t>6.9236</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>09 Feb 2026</t>
+          <t>27 Feb 2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>6.9523</t>
+          <t>6.9228</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>06 Feb 2026</t>
+          <t>26 Feb 2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>6.959</t>
+          <t>6.9228</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>05 Feb 2026</t>
+          <t>25 Feb 2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>6.957</t>
+          <t>6.9321</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>04 Feb 2026</t>
+          <t>24 Feb 2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>6.9533</t>
+          <t>6.9414</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>03 Feb 2026</t>
+          <t>13 Feb 2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>6.9608</t>
+          <t>6.9398</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>02 Feb 2026</t>
+          <t>12 Feb 2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>6.9695</t>
+          <t>6.9457</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>30 Jan 2026</t>
+          <t>11 Feb 2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>6.9678</t>
+          <t>6.9438</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>29 Jan 2026</t>
+          <t>10 Feb 2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>6.9771</t>
+          <t>6.9458</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>28 Jan 2026</t>
+          <t>09 Feb 2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>6.9755</t>
+          <t>6.9523</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>27 Jan 2026</t>
+          <t>06 Feb 2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>6.9858</t>
+          <t>6.959</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>26 Jan 2026</t>
+          <t>05 Feb 2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>6.9843</t>
+          <t>6.957</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>23 Jan 2026</t>
+          <t>04 Feb 2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>6.9929</t>
+          <t>6.9533</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>22 Jan 2026</t>
+          <t>03 Feb 2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>7.0019</t>
+          <t>6.9608</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>21 Jan 2026</t>
+          <t>02 Feb 2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>7.0014</t>
+          <t>6.9695</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>20 Jan 2026</t>
+          <t>30 Jan 2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>7.0006</t>
+          <t>6.9678</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>19 Jan 2026</t>
+          <t>29 Jan 2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>7.0051</t>
+          <t>6.9771</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>16 Jan 2026</t>
+          <t>28 Jan 2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>7.0078</t>
+          <t>6.9755</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>15 Jan 2026</t>
+          <t>27 Jan 2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>7.0064</t>
+          <t>6.9858</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>14 Jan 2026</t>
+          <t>26 Jan 2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>7.012</t>
+          <t>6.9843</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>13 Jan 2026</t>
+          <t>23 Jan 2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>7.0103</t>
+          <t>6.9929</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>12 Jan 2026</t>
+          <t>22 Jan 2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>7.0108</t>
+          <t>7.0019</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>09 Jan 2026</t>
+          <t>21 Jan 2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>7.0128</t>
+          <t>7.0014</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>08 Jan 2026</t>
+          <t>20 Jan 2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>7.0197</t>
+          <t>7.0006</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>07 Jan 2026</t>
+          <t>19 Jan 2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>7.0187</t>
+          <t>7.0051</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>06 Jan 2026</t>
+          <t>16 Jan 2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>7.0173</t>
+          <t>7.0078</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>05 Jan 2026</t>
+          <t>15 Jan 2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>7.023</t>
+          <t>7.0064</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
+          <t>14 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>7.012</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>13 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>7.0103</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>12 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>7.0108</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>09 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>7.0128</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>08 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>7.0197</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>07 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>7.0187</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>06 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>7.0173</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>05 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>7.023</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
           <t>Data source:</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr">
+      <c r="B110" t="inlineStr">
         <is>
           <t>China Foreign Exchange Trade System (CFETS)</t>
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" t="inlineStr"/>
-      <c r="B103" t="inlineStr">
+    <row r="111">
+      <c r="A111" t="inlineStr"/>
+      <c r="B111" t="inlineStr">
         <is>
           <t>www.chinamoney.com.cn/english/</t>
         </is>

--- a/backend/data/csv_import/Central_Parity_Historical_Data_2026.xlsx
+++ b/backend/data/csv_import/Central_Parity_Historical_Data_2026.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B111"/>
+  <dimension ref="A1:B117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -431,55 +431,55 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>17 Jun 2026</t>
+          <t>26 Jun 2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>6.8096</t>
+          <t>6.8166</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>16 Jun 2026</t>
+          <t>25 Jun 2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>6.8108</t>
+          <t>6.8209</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>15 Jun 2026</t>
+          <t>24 Jun 2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>6.8088</t>
+          <t>6.8195</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>12 Jun 2026</t>
+          <t>23 Jun 2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6.8109</t>
+          <t>6.8171</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>11 Jun 2026</t>
+          <t>22 Jun 2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -491,7 +491,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10 Jun 2026</t>
+          <t>18 Jun 2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -503,775 +503,775 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09 Jun 2026</t>
+          <t>17 Jun 2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>6.8147</t>
+          <t>6.8096</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>08 Jun 2026</t>
+          <t>16 Jun 2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>6.8198</t>
+          <t>6.8108</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>05 Jun 2026</t>
+          <t>15 Jun 2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>6.8157</t>
+          <t>6.8088</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>04 Jun 2026</t>
+          <t>12 Jun 2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>6.8203</t>
+          <t>6.8109</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>03 Jun 2026</t>
+          <t>11 Jun 2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>6.8184</t>
+          <t>6.815</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>02 Jun 2026</t>
+          <t>10 Jun 2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>6.8187</t>
+          <t>6.813</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>01 Jun 2026</t>
+          <t>09 Jun 2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>6.8167</t>
+          <t>6.8147</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>29 May 2026</t>
+          <t>08 Jun 2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>6.8176</t>
+          <t>6.8198</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>28 May 2026</t>
+          <t>05 Jun 2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>6.824</t>
+          <t>6.8157</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>27 May 2026</t>
+          <t>04 Jun 2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>6.8291</t>
+          <t>6.8203</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>26 May 2026</t>
+          <t>03 Jun 2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>6.8288</t>
+          <t>6.8184</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>25 May 2026</t>
+          <t>02 Jun 2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>6.8318</t>
+          <t>6.8187</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>22 May 2026</t>
+          <t>01 Jun 2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>6.8373</t>
+          <t>6.8167</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>21 May 2026</t>
+          <t>29 May 2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>6.8349</t>
+          <t>6.8176</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>20 May 2026</t>
+          <t>28 May 2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>6.8397</t>
+          <t>6.824</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>19 May 2026</t>
+          <t>27 May 2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>6.8375</t>
+          <t>6.8291</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>18 May 2026</t>
+          <t>26 May 2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>6.8435</t>
+          <t>6.8288</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>15 May 2026</t>
+          <t>25 May 2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>6.8415</t>
+          <t>6.8318</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>14 May 2026</t>
+          <t>22 May 2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>6.8401</t>
+          <t>6.8373</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>13 May 2026</t>
+          <t>21 May 2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>6.8431</t>
+          <t>6.8349</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>12 May 2026</t>
+          <t>20 May 2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>6.8426</t>
+          <t>6.8397</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>11 May 2026</t>
+          <t>19 May 2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>6.8467</t>
+          <t>6.8375</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>08 May 2026</t>
+          <t>18 May 2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>6.8502</t>
+          <t>6.8435</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07 May 2026</t>
+          <t>15 May 2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>6.8487</t>
+          <t>6.8415</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>06 May 2026</t>
+          <t>14 May 2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>6.8562</t>
+          <t>6.8401</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>30 Apr 2026</t>
+          <t>13 May 2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>6.8628</t>
+          <t>6.8431</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>29 Apr 2026</t>
+          <t>12 May 2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>6.8608</t>
+          <t>6.8426</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>28 Apr 2026</t>
+          <t>11 May 2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>6.8589</t>
+          <t>6.8467</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>27 Apr 2026</t>
+          <t>08 May 2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>6.8579</t>
+          <t>6.8502</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>24 Apr 2026</t>
+          <t>07 May 2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>6.8674</t>
+          <t>6.8487</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>23 Apr 2026</t>
+          <t>06 May 2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>6.865</t>
+          <t>6.8562</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>22 Apr 2026</t>
+          <t>30 Apr 2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>6.8635</t>
+          <t>6.8628</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>21 Apr 2026</t>
+          <t>29 Apr 2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>6.8594</t>
+          <t>6.8608</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>20 Apr 2026</t>
+          <t>28 Apr 2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>6.8648</t>
+          <t>6.8589</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>17 Apr 2026</t>
+          <t>27 Apr 2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>6.8622</t>
+          <t>6.8579</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>16 Apr 2026</t>
+          <t>24 Apr 2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>6.8616</t>
+          <t>6.8674</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>15 Apr 2026</t>
+          <t>23 Apr 2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>6.8582</t>
+          <t>6.865</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>14 Apr 2026</t>
+          <t>22 Apr 2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>6.8593</t>
+          <t>6.8635</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>13 Apr 2026</t>
+          <t>21 Apr 2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>6.8657</t>
+          <t>6.8594</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>10 Apr 2026</t>
+          <t>20 Apr 2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>6.8654</t>
+          <t>6.8648</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>09 Apr 2026</t>
+          <t>17 Apr 2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>6.8649</t>
+          <t>6.8622</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>08 Apr 2026</t>
+          <t>16 Apr 2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>6.868</t>
+          <t>6.8616</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07 Apr 2026</t>
+          <t>15 Apr 2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>6.8854</t>
+          <t>6.8582</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>03 Apr 2026</t>
+          <t>14 Apr 2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>6.8929</t>
+          <t>6.8593</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>02 Apr 2026</t>
+          <t>13 Apr 2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>6.888</t>
+          <t>6.8657</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>01 Apr 2026</t>
+          <t>10 Apr 2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>6.9025</t>
+          <t>6.8654</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>31 Mar 2026</t>
+          <t>09 Apr 2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>6.9194</t>
+          <t>6.8649</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>30 Mar 2026</t>
+          <t>08 Apr 2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>6.9223</t>
+          <t>6.868</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>27 Mar 2026</t>
+          <t>07 Apr 2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>6.9141</t>
+          <t>6.8854</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>26 Mar 2026</t>
+          <t>03 Apr 2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>6.9056</t>
+          <t>6.8929</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>25 Mar 2026</t>
+          <t>02 Apr 2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>6.8911</t>
+          <t>6.888</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>24 Mar 2026</t>
+          <t>01 Apr 2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>6.8943</t>
+          <t>6.9025</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>23 Mar 2026</t>
+          <t>31 Mar 2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>6.9041</t>
+          <t>6.9194</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>20 Mar 2026</t>
+          <t>30 Mar 2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>6.8898</t>
+          <t>6.9223</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>19 Mar 2026</t>
+          <t>27 Mar 2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>6.8975</t>
+          <t>6.9141</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>18 Mar 2026</t>
+          <t>26 Mar 2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>6.8909</t>
+          <t>6.9056</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>17 Mar 2026</t>
+          <t>25 Mar 2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>6.8961</t>
+          <t>6.8911</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>16 Mar 2026</t>
+          <t>24 Mar 2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>6.9057</t>
+          <t>6.8943</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>13 Mar 2026</t>
+          <t>23 Mar 2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>6.9007</t>
+          <t>6.9041</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>12 Mar 2026</t>
+          <t>20 Mar 2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>6.8959</t>
+          <t>6.8898</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>11 Mar 2026</t>
+          <t>19 Mar 2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>6.8917</t>
+          <t>6.8975</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>10 Mar 2026</t>
+          <t>18 Mar 2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>6.8982</t>
+          <t>6.8909</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>09 Mar 2026</t>
+          <t>17 Mar 2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>6.9158</t>
+          <t>6.8961</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>06 Mar 2026</t>
+          <t>16 Mar 2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>6.9025</t>
+          <t>6.9057</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>05 Mar 2026</t>
+          <t>13 Mar 2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -1283,462 +1283,534 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>04 Mar 2026</t>
+          <t>12 Mar 2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>6.9124</t>
+          <t>6.8959</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>03 Mar 2026</t>
+          <t>11 Mar 2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>6.9088</t>
+          <t>6.8917</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>02 Mar 2026</t>
+          <t>10 Mar 2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>6.9236</t>
+          <t>6.8982</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>27 Feb 2026</t>
+          <t>09 Mar 2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>6.9228</t>
+          <t>6.9158</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>26 Feb 2026</t>
+          <t>06 Mar 2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>6.9228</t>
+          <t>6.9025</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>25 Feb 2026</t>
+          <t>05 Mar 2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>6.9321</t>
+          <t>6.9007</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>24 Feb 2026</t>
+          <t>04 Mar 2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>6.9414</t>
+          <t>6.9124</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>13 Feb 2026</t>
+          <t>03 Mar 2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>6.9398</t>
+          <t>6.9088</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>12 Feb 2026</t>
+          <t>02 Mar 2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>6.9457</t>
+          <t>6.9236</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>11 Feb 2026</t>
+          <t>27 Feb 2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>6.9438</t>
+          <t>6.9228</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>10 Feb 2026</t>
+          <t>26 Feb 2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>6.9458</t>
+          <t>6.9228</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>09 Feb 2026</t>
+          <t>25 Feb 2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>6.9523</t>
+          <t>6.9321</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>06 Feb 2026</t>
+          <t>24 Feb 2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>6.959</t>
+          <t>6.9414</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>05 Feb 2026</t>
+          <t>13 Feb 2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>6.957</t>
+          <t>6.9398</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>04 Feb 2026</t>
+          <t>12 Feb 2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>6.9533</t>
+          <t>6.9457</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>03 Feb 2026</t>
+          <t>11 Feb 2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>6.9608</t>
+          <t>6.9438</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>02 Feb 2026</t>
+          <t>10 Feb 2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>6.9695</t>
+          <t>6.9458</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>30 Jan 2026</t>
+          <t>09 Feb 2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>6.9678</t>
+          <t>6.9523</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>29 Jan 2026</t>
+          <t>06 Feb 2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>6.9771</t>
+          <t>6.959</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>28 Jan 2026</t>
+          <t>05 Feb 2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>6.9755</t>
+          <t>6.957</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>27 Jan 2026</t>
+          <t>04 Feb 2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>6.9858</t>
+          <t>6.9533</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>26 Jan 2026</t>
+          <t>03 Feb 2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>6.9843</t>
+          <t>6.9608</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>23 Jan 2026</t>
+          <t>02 Feb 2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>6.9929</t>
+          <t>6.9695</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>22 Jan 2026</t>
+          <t>30 Jan 2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>7.0019</t>
+          <t>6.9678</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>21 Jan 2026</t>
+          <t>29 Jan 2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>7.0014</t>
+          <t>6.9771</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>20 Jan 2026</t>
+          <t>28 Jan 2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>7.0006</t>
+          <t>6.9755</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>19 Jan 2026</t>
+          <t>27 Jan 2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>7.0051</t>
+          <t>6.9858</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>16 Jan 2026</t>
+          <t>26 Jan 2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>7.0078</t>
+          <t>6.9843</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>15 Jan 2026</t>
+          <t>23 Jan 2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>7.0064</t>
+          <t>6.9929</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>14 Jan 2026</t>
+          <t>22 Jan 2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>7.012</t>
+          <t>7.0019</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>13 Jan 2026</t>
+          <t>21 Jan 2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>7.0103</t>
+          <t>7.0014</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>12 Jan 2026</t>
+          <t>20 Jan 2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>7.0108</t>
+          <t>7.0006</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>09 Jan 2026</t>
+          <t>19 Jan 2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>7.0128</t>
+          <t>7.0051</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>08 Jan 2026</t>
+          <t>16 Jan 2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>7.0197</t>
+          <t>7.0078</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>07 Jan 2026</t>
+          <t>15 Jan 2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>7.0187</t>
+          <t>7.0064</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>06 Jan 2026</t>
+          <t>14 Jan 2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>7.0173</t>
+          <t>7.012</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>05 Jan 2026</t>
+          <t>13 Jan 2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>7.023</t>
+          <t>7.0103</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
+          <t>12 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>7.0108</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>09 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>7.0128</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>08 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>7.0197</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>07 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>7.0187</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>06 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>7.0173</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>05 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>7.023</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
           <t>Data source:</t>
         </is>
       </c>
-      <c r="B110" t="inlineStr">
+      <c r="B116" t="inlineStr">
         <is>
           <t>China Foreign Exchange Trade System (CFETS)</t>
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" t="inlineStr"/>
-      <c r="B111" t="inlineStr">
+    <row r="117">
+      <c r="A117" t="inlineStr"/>
+      <c r="B117" t="inlineStr">
         <is>
           <t>www.chinamoney.com.cn/english/</t>
         </is>

--- a/backend/data/csv_import/Central_Parity_Historical_Data_2026.xlsx
+++ b/backend/data/csv_import/Central_Parity_Historical_Data_2026.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B117"/>
+  <dimension ref="A1:B137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -431,1386 +431,1626 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>26 Jun 2026</t>
+          <t>24 Jul 2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>6.8166</t>
+          <t>6.7939</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>25 Jun 2026</t>
+          <t>23 Jul 2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>6.8209</t>
+          <t>6.7906</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>24 Jun 2026</t>
+          <t>22 Jul 2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>6.8195</t>
+          <t>6.7933</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>23 Jun 2026</t>
+          <t>21 Jul 2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6.8171</t>
+          <t>6.7917</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>22 Jun 2026</t>
+          <t>20 Jul 2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>6.815</t>
+          <t>6.7948</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>18 Jun 2026</t>
+          <t>17 Jul 2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>6.813</t>
+          <t>6.7934</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>17 Jun 2026</t>
+          <t>16 Jul 2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>6.8096</t>
+          <t>6.7909</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>16 Jun 2026</t>
+          <t>15 Jul 2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>6.8108</t>
+          <t>6.791</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>15 Jun 2026</t>
+          <t>14 Jul 2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>6.8088</t>
+          <t>6.799</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>12 Jun 2026</t>
+          <t>13 Jul 2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>6.8109</t>
+          <t>6.7972</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>11 Jun 2026</t>
+          <t>10 Jul 2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>6.815</t>
+          <t>6.7989</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10 Jun 2026</t>
+          <t>09 Jul 2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>6.813</t>
+          <t>6.8036</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09 Jun 2026</t>
+          <t>08 Jul 2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>6.8147</t>
+          <t>6.8077</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>08 Jun 2026</t>
+          <t>07 Jul 2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>6.8198</t>
+          <t>6.8054</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>05 Jun 2026</t>
+          <t>06 Jul 2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>6.8157</t>
+          <t>6.8066</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>04 Jun 2026</t>
+          <t>03 Jul 2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>6.8203</t>
+          <t>6.8047</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>03 Jun 2026</t>
+          <t>02 Jul 2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>6.8184</t>
+          <t>6.8088</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>02 Jun 2026</t>
+          <t>01 Jul 2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>6.8187</t>
+          <t>6.8067</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>01 Jun 2026</t>
+          <t>30 Jun 2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>6.8167</t>
+          <t>6.8109</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>29 May 2026</t>
+          <t>29 Jun 2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>6.8176</t>
+          <t>6.8175</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>28 May 2026</t>
+          <t>26 Jun 2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>6.824</t>
+          <t>6.8166</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>27 May 2026</t>
+          <t>25 Jun 2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>6.8291</t>
+          <t>6.8209</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>26 May 2026</t>
+          <t>24 Jun 2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>6.8288</t>
+          <t>6.8195</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>25 May 2026</t>
+          <t>23 Jun 2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>6.8318</t>
+          <t>6.8171</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>22 May 2026</t>
+          <t>22 Jun 2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>6.8373</t>
+          <t>6.815</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>21 May 2026</t>
+          <t>18 Jun 2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>6.8349</t>
+          <t>6.813</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>20 May 2026</t>
+          <t>17 Jun 2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>6.8397</t>
+          <t>6.8096</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>19 May 2026</t>
+          <t>16 Jun 2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>6.8375</t>
+          <t>6.8108</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>18 May 2026</t>
+          <t>15 Jun 2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>6.8435</t>
+          <t>6.8088</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>15 May 2026</t>
+          <t>12 Jun 2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>6.8415</t>
+          <t>6.8109</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>14 May 2026</t>
+          <t>11 Jun 2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>6.8401</t>
+          <t>6.815</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>13 May 2026</t>
+          <t>10 Jun 2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>6.8431</t>
+          <t>6.813</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>12 May 2026</t>
+          <t>09 Jun 2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>6.8426</t>
+          <t>6.8147</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>11 May 2026</t>
+          <t>08 Jun 2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>6.8467</t>
+          <t>6.8198</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>08 May 2026</t>
+          <t>05 Jun 2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>6.8502</t>
+          <t>6.8157</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07 May 2026</t>
+          <t>04 Jun 2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>6.8487</t>
+          <t>6.8203</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>06 May 2026</t>
+          <t>03 Jun 2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>6.8562</t>
+          <t>6.8184</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>30 Apr 2026</t>
+          <t>02 Jun 2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>6.8628</t>
+          <t>6.8187</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>29 Apr 2026</t>
+          <t>01 Jun 2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>6.8608</t>
+          <t>6.8167</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>28 Apr 2026</t>
+          <t>29 May 2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>6.8589</t>
+          <t>6.8176</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>27 Apr 2026</t>
+          <t>28 May 2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>6.8579</t>
+          <t>6.824</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>24 Apr 2026</t>
+          <t>27 May 2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>6.8674</t>
+          <t>6.8291</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>23 Apr 2026</t>
+          <t>26 May 2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>6.865</t>
+          <t>6.8288</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>22 Apr 2026</t>
+          <t>25 May 2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>6.8635</t>
+          <t>6.8318</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>21 Apr 2026</t>
+          <t>22 May 2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>6.8594</t>
+          <t>6.8373</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>20 Apr 2026</t>
+          <t>21 May 2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>6.8648</t>
+          <t>6.8349</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>17 Apr 2026</t>
+          <t>20 May 2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>6.8622</t>
+          <t>6.8397</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>16 Apr 2026</t>
+          <t>19 May 2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>6.8616</t>
+          <t>6.8375</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>15 Apr 2026</t>
+          <t>18 May 2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>6.8582</t>
+          <t>6.8435</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>14 Apr 2026</t>
+          <t>15 May 2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>6.8593</t>
+          <t>6.8415</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>13 Apr 2026</t>
+          <t>14 May 2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>6.8657</t>
+          <t>6.8401</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>10 Apr 2026</t>
+          <t>13 May 2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>6.8654</t>
+          <t>6.8431</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>09 Apr 2026</t>
+          <t>12 May 2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>6.8649</t>
+          <t>6.8426</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>08 Apr 2026</t>
+          <t>11 May 2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>6.868</t>
+          <t>6.8467</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>07 Apr 2026</t>
+          <t>08 May 2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>6.8854</t>
+          <t>6.8502</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>03 Apr 2026</t>
+          <t>07 May 2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>6.8929</t>
+          <t>6.8487</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>02 Apr 2026</t>
+          <t>06 May 2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>6.888</t>
+          <t>6.8562</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>01 Apr 2026</t>
+          <t>30 Apr 2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>6.9025</t>
+          <t>6.8628</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>31 Mar 2026</t>
+          <t>29 Apr 2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>6.9194</t>
+          <t>6.8608</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>30 Mar 2026</t>
+          <t>28 Apr 2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>6.9223</t>
+          <t>6.8589</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>27 Mar 2026</t>
+          <t>27 Apr 2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>6.9141</t>
+          <t>6.8579</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>26 Mar 2026</t>
+          <t>24 Apr 2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>6.9056</t>
+          <t>6.8674</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>25 Mar 2026</t>
+          <t>23 Apr 2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>6.8911</t>
+          <t>6.865</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>24 Mar 2026</t>
+          <t>22 Apr 2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>6.8943</t>
+          <t>6.8635</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>23 Mar 2026</t>
+          <t>21 Apr 2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>6.9041</t>
+          <t>6.8594</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>20 Mar 2026</t>
+          <t>20 Apr 2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>6.8898</t>
+          <t>6.8648</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>19 Mar 2026</t>
+          <t>17 Apr 2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>6.8975</t>
+          <t>6.8622</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>18 Mar 2026</t>
+          <t>16 Apr 2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>6.8909</t>
+          <t>6.8616</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>17 Mar 2026</t>
+          <t>15 Apr 2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>6.8961</t>
+          <t>6.8582</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>16 Mar 2026</t>
+          <t>14 Apr 2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>6.9057</t>
+          <t>6.8593</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>13 Mar 2026</t>
+          <t>13 Apr 2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>6.9007</t>
+          <t>6.8657</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>12 Mar 2026</t>
+          <t>10 Apr 2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>6.8959</t>
+          <t>6.8654</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>11 Mar 2026</t>
+          <t>09 Apr 2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>6.8917</t>
+          <t>6.8649</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>10 Mar 2026</t>
+          <t>08 Apr 2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>6.8982</t>
+          <t>6.868</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>09 Mar 2026</t>
+          <t>07 Apr 2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>6.9158</t>
+          <t>6.8854</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>06 Mar 2026</t>
+          <t>03 Apr 2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>6.9025</t>
+          <t>6.8929</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>05 Mar 2026</t>
+          <t>02 Apr 2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>6.9007</t>
+          <t>6.888</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>04 Mar 2026</t>
+          <t>01 Apr 2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>6.9124</t>
+          <t>6.9025</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>03 Mar 2026</t>
+          <t>31 Mar 2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>6.9088</t>
+          <t>6.9194</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>02 Mar 2026</t>
+          <t>30 Mar 2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>6.9236</t>
+          <t>6.9223</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>27 Feb 2026</t>
+          <t>27 Mar 2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>6.9228</t>
+          <t>6.9141</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>26 Feb 2026</t>
+          <t>26 Mar 2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>6.9228</t>
+          <t>6.9056</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>25 Feb 2026</t>
+          <t>25 Mar 2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>6.9321</t>
+          <t>6.8911</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>24 Feb 2026</t>
+          <t>24 Mar 2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>6.9414</t>
+          <t>6.8943</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>13 Feb 2026</t>
+          <t>23 Mar 2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>6.9398</t>
+          <t>6.9041</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>12 Feb 2026</t>
+          <t>20 Mar 2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>6.9457</t>
+          <t>6.8898</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>11 Feb 2026</t>
+          <t>19 Mar 2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>6.9438</t>
+          <t>6.8975</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>10 Feb 2026</t>
+          <t>18 Mar 2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>6.9458</t>
+          <t>6.8909</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>09 Feb 2026</t>
+          <t>17 Mar 2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>6.9523</t>
+          <t>6.8961</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>06 Feb 2026</t>
+          <t>16 Mar 2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>6.959</t>
+          <t>6.9057</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>05 Feb 2026</t>
+          <t>13 Mar 2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>6.957</t>
+          <t>6.9007</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>04 Feb 2026</t>
+          <t>12 Mar 2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>6.9533</t>
+          <t>6.8959</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>03 Feb 2026</t>
+          <t>11 Mar 2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>6.9608</t>
+          <t>6.8917</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>02 Feb 2026</t>
+          <t>10 Mar 2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>6.9695</t>
+          <t>6.8982</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>30 Jan 2026</t>
+          <t>09 Mar 2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>6.9678</t>
+          <t>6.9158</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>29 Jan 2026</t>
+          <t>06 Mar 2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>6.9771</t>
+          <t>6.9025</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>28 Jan 2026</t>
+          <t>05 Mar 2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>6.9755</t>
+          <t>6.9007</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>27 Jan 2026</t>
+          <t>04 Mar 2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>6.9858</t>
+          <t>6.9124</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>26 Jan 2026</t>
+          <t>03 Mar 2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>6.9843</t>
+          <t>6.9088</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>23 Jan 2026</t>
+          <t>02 Mar 2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>6.9929</t>
+          <t>6.9236</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>22 Jan 2026</t>
+          <t>27 Feb 2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>7.0019</t>
+          <t>6.9228</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>21 Jan 2026</t>
+          <t>26 Feb 2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>7.0014</t>
+          <t>6.9228</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>20 Jan 2026</t>
+          <t>25 Feb 2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>7.0006</t>
+          <t>6.9321</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>19 Jan 2026</t>
+          <t>24 Feb 2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>7.0051</t>
+          <t>6.9414</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>16 Jan 2026</t>
+          <t>13 Feb 2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>7.0078</t>
+          <t>6.9398</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>15 Jan 2026</t>
+          <t>12 Feb 2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>7.0064</t>
+          <t>6.9457</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>14 Jan 2026</t>
+          <t>11 Feb 2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>7.012</t>
+          <t>6.9438</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>13 Jan 2026</t>
+          <t>10 Feb 2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>7.0103</t>
+          <t>6.9458</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>12 Jan 2026</t>
+          <t>09 Feb 2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>7.0108</t>
+          <t>6.9523</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>09 Jan 2026</t>
+          <t>06 Feb 2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>7.0128</t>
+          <t>6.959</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>08 Jan 2026</t>
+          <t>05 Feb 2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>7.0197</t>
+          <t>6.957</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>07 Jan 2026</t>
+          <t>04 Feb 2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>7.0187</t>
+          <t>6.9533</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>06 Jan 2026</t>
+          <t>03 Feb 2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>7.0173</t>
+          <t>6.9608</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>05 Jan 2026</t>
+          <t>02 Feb 2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>7.023</t>
+          <t>6.9695</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
+          <t>30 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>6.9678</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>29 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>6.9771</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>28 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>6.9755</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>27 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>6.9858</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>26 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>6.9843</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>23 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>6.9929</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>22 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>7.0019</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>21 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>7.0014</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>20 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>7.0006</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>19 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>7.0051</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>16 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>7.0078</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>15 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>7.0064</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>14 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>7.012</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>13 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>7.0103</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>12 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>7.0108</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>09 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>7.0128</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>08 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>7.0197</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>07 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>7.0187</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>06 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>7.0173</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>05 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>7.023</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
           <t>Data source:</t>
         </is>
       </c>
-      <c r="B116" t="inlineStr">
+      <c r="B136" t="inlineStr">
         <is>
           <t>China Foreign Exchange Trade System (CFETS)</t>
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" t="inlineStr"/>
-      <c r="B117" t="inlineStr">
+    <row r="137">
+      <c r="A137" t="inlineStr"/>
+      <c r="B137" t="inlineStr">
         <is>
           <t>www.chinamoney.com.cn/english/</t>
         </is>
